--- a/w4-generic-etl-framework/high_level_design.xlsx
+++ b/w4-generic-etl-framework/high_level_design.xlsx
@@ -108,7 +108,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -171,6 +171,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF6"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -342,6 +347,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3073,7 +3084,7 @@
     <row r="5" ht="74" customHeight="1" s="24">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>19 PRESENT  (35%)   ·   7 PARTIAL  (13%)   ·   27 MISSING  (50%)   ·   1 UNCONFIRMED        The missing half is NOT spread evenly. It clusters in two categories: KEYS AND TABLE STRUCTURE, where ABC holds nothing at all - no primary key, no business key, no surrogate key, no SCD2 date columns - and SEQUENCING AND SCOPE. ABC works today because every one of those lives inside hand-written mapping SQL. The moment the framework becomes configuration driven, they all become configuration. The audit, quality and reconciliation machinery, by contrast, is largely reusable as it stands.</t>
+          <t>19 PRESENT  ·  7 PARTIAL  ·  26 MISSING  ·  1 OUT OF SCOPE  ·  1 UNCONFIRMED        The missing half is NOT spread evenly. It clusters in two categories: KEYS AND TABLE STRUCTURE, where ABC holds nothing at all - no primary key, no business key, no surrogate key, no SCD2 date columns - and SEQUENCING AND SCOPE. ABC works today because every one of those lives inside hand-written mapping SQL. The moment the framework becomes configuration driven, they all become configuration. The audit, quality and reconciliation machinery, by contrast, is largely reusable as it stands.</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3217,7 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>Needed for the upstream readiness check, and for source-to-target lineage</t>
+          <t>Needed for the upstream readiness check at T3. NOTE: this is a READINESS list, not a lineage list - the tables whose completion gates this load. It is NOT the set of tables the team SQL joins, and the two are not meant to be equal. A static reference table the SQL joins gates nothing and does not belong here. HQ-09.</t>
         </is>
       </c>
       <c r="E10" s="35" t="inlineStr">
@@ -3761,7 +3772,7 @@
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>A table whose SQL looks up another Zone 2 table cannot load before it. Agreed mechanism: at load start a table reads the prerequisite metadata, checks each prerequisite status for this run, and proceeds only when all are complete</t>
+          <t>A table whose SQL looks up another Zone 2 table cannot load before it. Mechanism: prerequisites are DECLARED in metadata (HQ-08, not derived from the SQL - a join is not a prerequisite). B7 resolves them into an attempt order; T2 then checks each prerequisite status for this run and proceeds only when all are Completed. Prerequisites are always inside the same batch (HQ-07, assumption).</t>
         </is>
       </c>
       <c r="E25" s="37" t="inlineStr">
@@ -3909,12 +3920,12 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>A prerequisite outside the batch cannot be resolved inside the run, so it has to become a batch-level dependency instead</t>
-        </is>
-      </c>
-      <c r="E29" s="37" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>CLOSED BY THE HQ-07 ASSUMPTION. Prerequisites are always inside the same batch, so a cross-batch need is expressed as a batch-level dependency for Stonebranch rather than as a prerequisite inside the run. The escape hatch is named so nobody has to rediscover it.</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE</t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
@@ -5019,7 +5030,7 @@
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>Catch a cycle in the prerequisites, a member with no pipeline, a strategy illegal for its table type. SQL and mapping validity is explicitly OUT OF SCOPE - that is build</t>
+          <t>Catch a cycle in the prerequisites, a member with no pipeline, a strategy illegal for its table type, and - the rule that defends HQ-07 - a declared prerequisite that is not an active member of THIS batch. SQL and mapping validity is explicitly OUT OF SCOPE; that is build (R-12).</t>
         </is>
       </c>
       <c r="E59" s="37" t="inlineStr">
@@ -5133,7 +5144,7 @@
     <col width="72" customWidth="1" style="24" min="2" max="2"/>
     <col width="86" customWidth="1" style="24" min="3" max="3"/>
     <col width="24" customWidth="1" style="24" min="4" max="4"/>
-    <col width="34" customWidth="1" style="24" min="5" max="5"/>
+    <col width="96" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" s="24">
@@ -5313,7 +5324,11 @@
           <t>B4, B7</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by HQ-08.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
@@ -5336,7 +5351,11 @@
           <t>B2, B7, T2</t>
         </is>
       </c>
-      <c r="E10" s="39" t="n"/>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>ASSUMPTION — YES, prerequisites are always inside the same batch. Taken to close the design rather than verified. It is DEFENDED, not merely assumed: B5 rejects any configuration whose declared prerequisite is not an active member of the same batch, so the assumption cannot rot silently. Consequence worth stating — batch membership stops being a purely operational grouping. Two tables in a prerequisite relationship MUST be co-batched, so the dependency graph now constrains how batches are composed. A genuine cross-batch need becomes a batch-level dependency for Stonebranch instead (F-22, now out of scope).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -5359,7 +5378,11 @@
           <t>B4, B7</t>
         </is>
       </c>
-      <c r="E11" s="39" t="n"/>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>PROPOSED — DECLARED by hand, validated by the framework. This REVERSES the lean toward derived stated when the question was raised. Three reasons: (1) a JOIN IS NOT A PREREQUISITE — a lookup against a static reference table is a join that needs no ordering, and only the author knows which joins must be sequenced; (2) derived edges still have to be stored and refreshed when the SQL changes, so the drift exposure does not actually go away; (3) it needs SQL parsing or query-history introspection, which is machinery for a problem that declaration plus B5 validation already solves. What makes declaration safe is the B5 rule from HQ-07: every declared prerequisite must be an active member of this batch.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -5382,7 +5405,11 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="E12" s="39" t="n"/>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>PROPOSED — DISSOLVED by reframing what the declared source list is FOR. It is not a lineage list and was never meant to equal the set of tables the SQL touches. It is a READINESS list: the tables whose completion gates this load. A static reference table the SQL joins gates nothing and does not belong on it. So the two lists diverging is not drift — they were never the same set. The residual risk, someone adding a join to a table that DOES gate and not declaring it, is a build and review concern, which is where R-12 already puts it.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
